--- a/ARQUIVOS_GERADOS/extratos_corte.xlsx
+++ b/ARQUIVOS_GERADOS/extratos_corte.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S56"/>
+  <dimension ref="A1:S32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,53 +521,53 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="B2" t="n">
-        <v>854204</v>
+        <v>854546</v>
       </c>
       <c r="C2" t="n">
-        <v>473954</v>
+        <v>476816</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ALIM MAT NESTLE 210GR NESCAU CEREAL</t>
+          <t>PAO BISNAGUINHA VISCONTI 240GR</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5374008684</v>
+        <v>2371039072</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>44,28</t>
+          <t>141,12</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J2" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="K2" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>44.28</v>
+        <v>35.28</v>
       </c>
       <c r="N2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="O2" t="n">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -584,63 +584,63 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>16:43</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="B3" t="n">
-        <v>854285</v>
+        <v>854509</v>
       </c>
       <c r="C3" t="n">
-        <v>475668</v>
+        <v>470842</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CHOC FERRERO KINDER BUENO WHITE 39GR T2</t>
+          <t>ACHOC NESCAU 730GR SACHET</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>421247096</v>
+        <v>99046723</v>
       </c>
       <c r="F3" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4.770,40</t>
+          <t>21,18</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="I3" t="n">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="J3" t="n">
         <v>102</v>
       </c>
       <c r="K3" t="n">
-        <v>571</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>4770.4</v>
+        <v>21.18</v>
       </c>
       <c r="N3" t="n">
         <v>11</v>
       </c>
       <c r="O3" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>MERCADORIA PROXIMO AO VENCIMENTO</t>
+          <t>QUANTIDADE INFERIOR DA OS</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -653,63 +653,63 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>11:15</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="B4" t="n">
-        <v>854284</v>
+        <v>854546</v>
       </c>
       <c r="C4" t="n">
-        <v>443449</v>
+        <v>427994</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CHOC LACTA AO LEITE 20GR</t>
+          <t>AZEITE E VIRG PORT ANDORINHA 500ML VIDRO</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>421247052</v>
+        <v>2371039083</v>
       </c>
       <c r="F4" t="n">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1.683,60</t>
+          <t>83,91</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I4" t="n">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="J4" t="n">
         <v>101</v>
       </c>
       <c r="K4" t="n">
-        <v>4.33</v>
+        <v>34</v>
       </c>
       <c r="L4" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>673.4400000000001</v>
+        <v>83.91</v>
       </c>
       <c r="N4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="O4" t="n">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>MERCADORIA PROXIMO AO VENCIMENTO</t>
+          <t>QUANTIDADE INFERIOR DA OS</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -722,59 +722,59 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:51</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="B5" t="n">
-        <v>854345</v>
+        <v>854435</v>
       </c>
       <c r="C5" t="n">
-        <v>465372</v>
+        <v>427994</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CHOC FERRERO KINDER BUENO WHITE 39GR T2</t>
+          <t>AZEITE E VIRG PORT ANDORINHA 500ML VIDRO</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5422004511</v>
+        <v>7153000103</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>480</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>275,31</t>
+          <t>12.739,20</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="I5" t="n">
         <v>6</v>
       </c>
       <c r="J5" t="n">
-        <v>273</v>
+        <v>101</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>252</v>
       </c>
       <c r="M5" t="n">
-        <v>275.31</v>
+        <v>6688.08</v>
       </c>
       <c r="N5" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="O5" t="n">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -782,72 +782,72 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>122537</v>
+        <v>180101</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>YAGO RODRIGUES DA SILVA</t>
+          <t>CARLOS ALBERTO SANTOS DA SILVA FILHO</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>22:49</t>
+          <t>11:12</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="B6" t="n">
-        <v>854285</v>
+        <v>854551</v>
       </c>
       <c r="C6" t="n">
-        <v>472269</v>
+        <v>463671</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CHOC PECCIN TRENTO 16X29GR CHOC BRANCO</t>
+          <t>SABAO PO ASSIM 800GR BICARBONATO</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>421247084</v>
+        <v>2557057589</v>
       </c>
       <c r="F6" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2.968,80</t>
+          <t>144,21</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I6" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="J6" t="n">
         <v>101</v>
       </c>
       <c r="K6" t="n">
-        <v>3.786</v>
+        <v>6</v>
       </c>
       <c r="L6" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>2968.8</v>
+        <v>144.21</v>
       </c>
       <c r="N6" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="O6" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>MERCADORIA PROXIMO AO VENCIMENTO</t>
+          <t>QUANTIDADE INFERIOR DA OS</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -860,59 +860,59 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>17:02</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="B7" t="n">
-        <v>854320</v>
+        <v>854555</v>
       </c>
       <c r="C7" t="n">
-        <v>462101</v>
+        <v>465372</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CAIXA ARQUIVO MORTO FRAMA PAP 25X35,5CM</t>
+          <t>CHOC FERRERO KINDER BUENO WHITE 39GR T2</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2477024150</v>
+        <v>7154000035</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>104,78</t>
+          <t>81,89</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="I7" t="n">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="J7" t="n">
-        <v>102</v>
+        <v>273</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>104.78</v>
+        <v>81.89</v>
       </c>
       <c r="N7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O7" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -929,59 +929,59 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:25</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="B8" t="n">
-        <v>854202</v>
+        <v>854502</v>
       </c>
       <c r="C8" t="n">
-        <v>470878</v>
+        <v>420215</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FITA ADES EMPAC TEK BOND TRANSP 48MMX40M</t>
+          <t>BALAO SAO ROQUE 7 ROSA TUTI FRUTI 50UN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5374008720</v>
+        <v>5157004873</v>
       </c>
       <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>77,13</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>18</v>
+      </c>
+      <c r="I8" t="n">
+        <v>29</v>
+      </c>
+      <c r="J8" t="n">
+        <v>102</v>
+      </c>
+      <c r="K8" t="n">
         <v>3</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>35,76</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>28</v>
-      </c>
-      <c r="I8" t="n">
-        <v>19</v>
-      </c>
-      <c r="J8" t="n">
-        <v>101</v>
-      </c>
-      <c r="K8" t="n">
-        <v>10</v>
-      </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>35.76</v>
+        <v>77.13</v>
       </c>
       <c r="N8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -989,68 +989,68 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>100879</v>
+        <v>122537</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>CLEITON BATISTA SIDNEI</t>
+          <t>YAGO RODRIGUES DA SILVA</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>00:50</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="B9" t="n">
-        <v>854344</v>
+        <v>854478</v>
       </c>
       <c r="C9" t="n">
-        <v>470878</v>
+        <v>423385</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FITA ADES EMPAC TEK BOND TRANSP 48MMX40M</t>
+          <t>COPO DESC COPOBRAS 200ML TRA 100UN PS</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1137044462</v>
+        <v>5055005120</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>11,50</t>
+          <t>99,79</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="I9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J9" t="n">
         <v>101</v>
       </c>
       <c r="K9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>99.79000000000001</v>
+      </c>
+      <c r="N9" t="n">
         <v>10</v>
       </c>
-      <c r="L9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M9" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="N9" t="n">
-        <v>21</v>
-      </c>
       <c r="O9" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -1058,68 +1058,68 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>180809</v>
+        <v>180101</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>GABRIELA DE SOUSA BEZERRA</t>
+          <t>CARLOS ALBERTO SANTOS DA SILVA FILHO</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>21:09</t>
+          <t>10:32</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="B10" t="n">
-        <v>854323</v>
+        <v>854496</v>
       </c>
       <c r="C10" t="n">
-        <v>477087</v>
+        <v>420215</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FRAC AMAC COMFORT 400ML SAC CONC F INTEN</t>
+          <t>BALAO SAO ROQUE 7 ROSA TUTI FRUTI 50UN</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7127001985</v>
+        <v>3965027900</v>
       </c>
       <c r="F10" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>67,56</t>
+          <t>83,64</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="I10" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="J10" t="n">
         <v>102</v>
       </c>
       <c r="K10" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L10" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>39.41</v>
+        <v>83.64</v>
       </c>
       <c r="N10" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="O10" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1136,59 +1136,59 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>10:47</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="B11" t="n">
-        <v>854204</v>
+        <v>854587</v>
       </c>
       <c r="C11" t="n">
-        <v>452248</v>
+        <v>476941</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>RODO STA MARIA DUPLO 60CM CABO METAL</t>
+          <t>CHOCOLATE NESTLE PRESTIGIO 33GR FUT VERM</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5374008684</v>
+        <v>5097012473</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>276,43</t>
+          <t>94,94</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I11" t="n">
-        <v>13</v>
+        <v>103</v>
       </c>
       <c r="J11" t="n">
         <v>101</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
         <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>276.43</v>
+        <v>94.94</v>
       </c>
       <c r="N11" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="O11" t="n">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1196,68 +1196,68 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>180101</v>
+        <v>180121</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO SANTOS DA SILVA FILHO</t>
+          <t>TAINA MEDEIROS RIBEIRO</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>22:17</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="B12" t="n">
-        <v>854360</v>
+        <v>854551</v>
       </c>
       <c r="C12" t="n">
-        <v>477087</v>
+        <v>448771</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FRAC AMAC COMFORT 400ML SAC CONC F INTEN</t>
+          <t>CREME TRAT SKALA 1KG JABORANDI</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5560002983</v>
+        <v>5049020306</v>
       </c>
       <c r="F12" t="n">
         <v>1</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>5,65</t>
+          <t>7,84</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="I12" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>102</v>
+        <v>403</v>
       </c>
       <c r="K12" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L12" t="n">
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>5.65</v>
+        <v>7.84</v>
       </c>
       <c r="N12" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="O12" t="n">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -1265,68 +1265,68 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>122537</v>
+        <v>180101</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>YAGO RODRIGUES DA SILVA</t>
+          <t>CARLOS ALBERTO SANTOS DA SILVA FILHO</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>22:56</t>
+          <t>13:45</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="B13" t="n">
-        <v>854404</v>
+        <v>854555</v>
       </c>
       <c r="C13" t="n">
-        <v>477087</v>
+        <v>449719</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FRAC AMAC COMFORT 400ML SAC CONC F INTEN</t>
+          <t>PALMITO PALMEIRAL ACAI INTEIRO 1,8KG</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5767001131</v>
+        <v>4591009852</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5,60</t>
+          <t>425,72</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="I13" t="n">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="J13" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K13" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M13" t="n">
-        <v>5.6</v>
+        <v>425.72</v>
       </c>
       <c r="N13" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="O13" t="n">
-        <v>56</v>
+        <v>7</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -1334,137 +1334,137 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>122537</v>
+        <v>122232</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>YAGO RODRIGUES DA SILVA</t>
+          <t>MARCELO RAMADA DE JESUS</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>22:56</t>
+          <t>18:07</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="B14" t="n">
-        <v>854285</v>
+        <v>854469</v>
       </c>
       <c r="C14" t="n">
-        <v>467047</v>
+        <v>455159</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LEITE COND PIRACANJUBA 2,5 KG  BAG</t>
+          <t>AMENDOIM BONISSIMO 1,010KG TORRADO GRANU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>421247086</v>
+        <v>5811001424</v>
       </c>
       <c r="F14" t="n">
-        <v>80</v>
+        <v>4</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2.348,80</t>
+          <t>108,48</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I14" t="n">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="J14" t="n">
         <v>102</v>
       </c>
       <c r="K14" t="n">
-        <v>596</v>
+        <v>19</v>
       </c>
       <c r="L14" t="n">
-        <v>80</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>2348.8</v>
+        <v>81.36</v>
       </c>
       <c r="N14" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="O14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>MERCADORIA PROXIMO AO VENCIMENTO</t>
+          <t>QUANTIDADE INFERIOR DA OS</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>180101</v>
+        <v>122537</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO SANTOS DA SILVA FILHO</t>
+          <t>YAGO RODRIGUES DA SILVA</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>02:11</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="B15" t="n">
-        <v>854230</v>
+        <v>854480</v>
       </c>
       <c r="C15" t="n">
-        <v>450207</v>
+        <v>476941</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MOLHO MADEIRA DEZ SACHET 300GR</t>
+          <t>CHOCOLATE NESTLE PRESTIGIO 33GR FUT VERM</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5420002986</v>
+        <v>3266031639</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>44,67</t>
+          <t>83,04</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>103</v>
       </c>
       <c r="J15" t="n">
-        <v>667</v>
+        <v>101</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
         <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>44.67</v>
+        <v>83.04000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O15" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -1481,59 +1481,59 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>11:56</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46132</v>
+        <v>46135</v>
       </c>
       <c r="B16" t="n">
-        <v>854210</v>
+        <v>854612</v>
       </c>
       <c r="C16" t="n">
-        <v>455588</v>
+        <v>459841</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>MOSTARDA HELLMANNS 1,01KG DOYPACK</t>
+          <t>AMENDOIM DORI 320GR ORIGINAL</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5213009712</v>
+        <v>4753005395</v>
       </c>
       <c r="F16" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>221,04</t>
+          <t>21,56</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I16" t="n">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="J16" t="n">
         <v>104</v>
       </c>
       <c r="K16" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L16" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="M16" t="n">
-        <v>184.2</v>
+        <v>21.56</v>
       </c>
       <c r="N16" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -1541,68 +1541,68 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>180101</v>
+        <v>122537</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO SANTOS DA SILVA FILHO</t>
+          <t>YAGO RODRIGUES DA SILVA</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>04:13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46132</v>
+        <v>46135</v>
       </c>
       <c r="B17" t="n">
-        <v>854319</v>
+        <v>854656</v>
       </c>
       <c r="C17" t="n">
-        <v>473258</v>
+        <v>455159</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VIN PORT JULIA FLORISTA TINTO 750ML</t>
+          <t>AMENDOIM BONISSIMO 1,010KG TORRADO GRANU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5049020214</v>
+        <v>5670002263</v>
       </c>
       <c r="F17" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>205,32</t>
+          <t>54,42</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I17" t="n">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="J17" t="n">
-        <v>204</v>
+        <v>102</v>
       </c>
       <c r="K17" t="n">
+        <v>19</v>
+      </c>
+      <c r="L17" t="n">
         <v>2</v>
       </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
       <c r="M17" t="n">
-        <v>34.22</v>
+        <v>54.42</v>
       </c>
       <c r="N17" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="O17" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -1610,68 +1610,68 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>180101</v>
+        <v>122537</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO SANTOS DA SILVA FILHO</t>
+          <t>YAGO RODRIGUES DA SILVA</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>04:55</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46132</v>
+        <v>46135</v>
       </c>
       <c r="B18" t="n">
-        <v>854360</v>
+        <v>854596</v>
       </c>
       <c r="C18" t="n">
-        <v>473610</v>
+        <v>459841</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>GELATINA SOL 20G MORANGO</t>
+          <t>AMENDOIM DORI 320GR ORIGINAL</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5560002980</v>
+        <v>1029073179</v>
       </c>
       <c r="F18" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>36,58</t>
+          <t>64,68</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I18" t="n">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="J18" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L18" t="n">
         <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>36.58</v>
+        <v>10.78</v>
       </c>
       <c r="N18" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="O18" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
@@ -1688,59 +1688,59 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>22:55</t>
+          <t>02:50</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46132</v>
+        <v>46135</v>
       </c>
       <c r="B19" t="n">
-        <v>854360</v>
+        <v>854594</v>
       </c>
       <c r="C19" t="n">
-        <v>473608</v>
+        <v>455159</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>GELATINA SOL 20G LIMAO</t>
+          <t>AMENDOIM BONISSIMO 1,010KG TORRADO GRANU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5560002980</v>
+        <v>4030016125</v>
       </c>
       <c r="F19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>36,00</t>
+          <t>49,80</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I19" t="n">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="J19" t="n">
         <v>102</v>
       </c>
       <c r="K19" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="L19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M19" t="n">
-        <v>36</v>
+        <v>49.8</v>
       </c>
       <c r="N19" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="O19" t="n">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -1757,263 +1757,263 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>23:04</t>
+          <t>01:59</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46132</v>
+        <v>46135</v>
       </c>
       <c r="B20" t="n">
-        <v>854228</v>
+        <v>854669</v>
       </c>
       <c r="C20" t="n">
-        <v>469498</v>
+        <v>461619</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>BISC MARIL LEV 110GR MAG TOAST INTEGRAL</t>
+          <t>UD TACA VDO AGUA NADIR 340ML BRISTO 0011</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1351075398</v>
+        <v>1353114349</v>
       </c>
       <c r="F20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>19,76</t>
+          <t>272,88</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="I20" t="n">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="J20" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="K20" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>9.880000000000001</v>
+        <v>136.44</v>
       </c>
       <c r="N20" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="O20" t="n">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>PRODUTO AVARIADO</t>
+          <t>QUANTIDADE INFERIOR DA OS</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>180101</v>
+        <v>122537</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO SANTOS DA SILVA FILHO</t>
+          <t>YAGO RODRIGUES DA SILVA</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>05:43</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46132</v>
+        <v>46135</v>
       </c>
       <c r="B21" t="n">
-        <v>854202</v>
+        <v>854670</v>
       </c>
       <c r="C21" t="n">
-        <v>470944</v>
+        <v>467985</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>AMEIXA SO FRUTA CALDA 150GR</t>
+          <t>FRALDA MAMYPOKO CALCA AZUL REGULAR RN 20</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5374008728</v>
+        <v>5597001225</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>124,54</t>
+          <t>128,83</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I21" t="n">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="J21" t="n">
         <v>103</v>
       </c>
       <c r="K21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>124.54</v>
+        <v>128.83</v>
       </c>
       <c r="N21" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O21" t="n">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>PRODUTO AVARIADO</t>
+          <t>QUANTIDADE INFERIOR DA OS</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>180101</v>
+        <v>122537</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO SANTOS DA SILVA FILHO</t>
+          <t>YAGO RODRIGUES DA SILVA</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>06:23</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46132</v>
+        <v>46135</v>
       </c>
       <c r="B22" t="n">
-        <v>854202</v>
+        <v>854673</v>
       </c>
       <c r="C22" t="n">
-        <v>431553</v>
+        <v>463671</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>DOCE LEITE ITAMBE LATA 800GR</t>
+          <t>SABAO PO ASSIM 800GR BICARBONATO</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5598001487</v>
+        <v>4124015977</v>
       </c>
       <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>381,35</t>
+          <t>142,66</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I22" t="n">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="J22" t="n">
         <v>101</v>
       </c>
       <c r="K22" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="L22" t="n">
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>381.35</v>
+        <v>142.66</v>
       </c>
       <c r="N22" t="n">
+        <v>3</v>
+      </c>
+      <c r="O22" t="n">
         <v>9</v>
       </c>
-      <c r="O22" t="n">
-        <v>57</v>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>PRODUTO AVARIADO</t>
+          <t>QUANTIDADE INFERIOR DA OS</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>180101</v>
+        <v>180121</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO SANTOS DA SILVA FILHO</t>
+          <t>TAINA MEDEIROS RIBEIRO</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>03:09</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46132</v>
+        <v>46135</v>
       </c>
       <c r="B23" t="n">
-        <v>854343</v>
+        <v>854637</v>
       </c>
       <c r="C23" t="n">
-        <v>467001</v>
+        <v>463671</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>CAFE CAPSULA NESCAFE D G 10X1 AU L BAUN</t>
+          <t>SABAO PO ASSIM 800GR BICARBONATO</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5370002836</v>
+        <v>1678075295</v>
       </c>
       <c r="F23" t="n">
         <v>1</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>21,57</t>
+          <t>132,12</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I23" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="J23" t="n">
-        <v>204</v>
+        <v>101</v>
       </c>
       <c r="K23" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L23" t="n">
         <v>1</v>
       </c>
       <c r="M23" t="n">
-        <v>21.57</v>
+        <v>132.12</v>
       </c>
       <c r="N23" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="O23" t="n">
         <v>16</v>
@@ -2024,122 +2024,122 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>181017</v>
+        <v>180121</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>TALITA DA SILVA OLIVEIRA</t>
+          <t>TAINA MEDEIROS RIBEIRO</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>02:16</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>46132</v>
+        <v>46135</v>
       </c>
       <c r="B24" t="n">
-        <v>854274</v>
+        <v>854658</v>
       </c>
       <c r="C24" t="n">
-        <v>431553</v>
+        <v>459841</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DOCE LEITE ITAMBE LATA 800GR</t>
+          <t>AMENDOIM DORI 320GR ORIGINAL</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5968000247</v>
+        <v>1664041413</v>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>370,31</t>
+          <t>65,34</t>
         </is>
       </c>
       <c r="H24" t="n">
+        <v>11</v>
+      </c>
+      <c r="I24" t="n">
+        <v>69</v>
+      </c>
+      <c r="J24" t="n">
+        <v>104</v>
+      </c>
+      <c r="K24" t="n">
+        <v>9</v>
+      </c>
+      <c r="L24" t="n">
         <v>6</v>
       </c>
-      <c r="I24" t="n">
-        <v>71</v>
-      </c>
-      <c r="J24" t="n">
-        <v>101</v>
-      </c>
-      <c r="K24" t="n">
-        <v>11</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1</v>
-      </c>
       <c r="M24" t="n">
-        <v>370.31</v>
+        <v>65.34</v>
       </c>
       <c r="N24" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="O24" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>PRODUTO AVARIADO</t>
+          <t>QUANTIDADE INFERIOR DA OS</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>180101</v>
+        <v>122537</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>CARLOS ALBERTO SANTOS DA SILVA FILHO</t>
+          <t>YAGO RODRIGUES DA SILVA</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>02:50</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>46132</v>
+        <v>46135</v>
       </c>
       <c r="B25" t="n">
-        <v>854402</v>
+        <v>854608</v>
       </c>
       <c r="C25" t="n">
-        <v>467001</v>
+        <v>436036</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>CAFE CAPSULA NESCAFE D G 10X1 AU L BAUN</t>
+          <t>SAND HAV BRASIL  LOGO BCO 35/6</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5662000961</v>
+        <v>5974000047</v>
       </c>
       <c r="F25" t="n">
         <v>3</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>59,01</t>
+          <t>121,44</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I25" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K25" t="n">
         <v>4</v>
@@ -2148,13 +2148,13 @@
         <v>3</v>
       </c>
       <c r="M25" t="n">
-        <v>59.01</v>
+        <v>121.44</v>
       </c>
       <c r="N25" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="O25" t="n">
-        <v>57</v>
+        <v>7</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
@@ -2162,68 +2162,68 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>181017</v>
+        <v>180185</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>TALITA DA SILVA OLIVEIRA</t>
+          <t>ALEANDRA TRINDADE SOUSA</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>21:57</t>
+          <t>02:07</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>46132</v>
+        <v>46135</v>
       </c>
       <c r="B26" t="n">
-        <v>854227</v>
+        <v>854608</v>
       </c>
       <c r="C26" t="n">
-        <v>467001</v>
+        <v>436036</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>CAFE CAPSULA NESCAFE D G 10X1 AU L BAUN</t>
+          <t>SAND HAV BRASIL  LOGO BCO 35/6</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5163007446</v>
+        <v>5974000051</v>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>37,10</t>
+          <t>41,24</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I26" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="J26" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K26" t="n">
         <v>4</v>
       </c>
       <c r="L26" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" t="n">
+        <v>41.24</v>
+      </c>
+      <c r="N26" t="n">
         <v>2</v>
       </c>
-      <c r="M26" t="n">
-        <v>37.1</v>
-      </c>
-      <c r="N26" t="n">
-        <v>11</v>
-      </c>
       <c r="O26" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -2231,68 +2231,68 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>180744</v>
+        <v>181255</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>TAYNARA PEREIRA DE ALMEIDA</t>
+          <t>DANIELE AIRES MOREIRA</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>02:55</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B27" t="n">
-        <v>854477</v>
+        <v>854595</v>
       </c>
       <c r="C27" t="n">
-        <v>465489</v>
+        <v>459742</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>CANETA ESF CIS SPIRO SORT 24UN</t>
+          <t>VIN NAC PERGOLA 750ML BCO SECO</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5875000562</v>
+        <v>5560002994</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>42,60</t>
+          <t>93,00</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="I27" t="n">
-        <v>8</v>
+        <v>106</v>
       </c>
       <c r="J27" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="K27" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="L27" t="n">
         <v>1</v>
       </c>
       <c r="M27" t="n">
-        <v>42.6</v>
+        <v>15.5</v>
       </c>
       <c r="N27" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="O27" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
@@ -2300,68 +2300,68 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>181203</v>
+        <v>180121</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>JANAINA SOUSA PAIXAO</t>
+          <t>TAINA MEDEIROS RIBEIRO</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>22:13</t>
+          <t>02:15</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B28" t="n">
-        <v>854476</v>
+        <v>854594</v>
       </c>
       <c r="C28" t="n">
-        <v>468667</v>
+        <v>420215</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>PACOCA ROLHA EMB MORENINHA DO RIO 300GR</t>
+          <t>BALAO SAO ROQUE 7 ROSA TUTI FRUTI 50UN</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5282003968</v>
+        <v>1591030747</v>
       </c>
       <c r="F28" t="n">
         <v>1</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>8,11</t>
+          <t>77,66</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="I28" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="J28" t="n">
         <v>102</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L28" t="n">
         <v>1</v>
       </c>
       <c r="M28" t="n">
-        <v>8.109999999999999</v>
+        <v>77.66</v>
       </c>
       <c r="N28" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
@@ -2378,38 +2378,38 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>21:03</t>
+          <t>00:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B29" t="n">
-        <v>854404</v>
+        <v>854629</v>
       </c>
       <c r="C29" t="n">
-        <v>431921</v>
+        <v>427994</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ENV FORONI BRANCO 24X34</t>
+          <t>AZEITE E VIRG PORT ANDORINHA 500ML VIDRO</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5982000148</v>
+        <v>4718014077</v>
       </c>
       <c r="F29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>112,41</t>
+          <t>82,35</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="I29" t="n">
         <v>6</v>
@@ -2418,19 +2418,19 @@
         <v>101</v>
       </c>
       <c r="K29" t="n">
+        <v>34</v>
+      </c>
+      <c r="L29" t="n">
+        <v>3</v>
+      </c>
+      <c r="M29" t="n">
+        <v>82.34999999999999</v>
+      </c>
+      <c r="N29" t="n">
         <v>4</v>
       </c>
-      <c r="L29" t="n">
-        <v>1</v>
-      </c>
-      <c r="M29" t="n">
-        <v>112.41</v>
-      </c>
-      <c r="N29" t="n">
-        <v>2</v>
-      </c>
       <c r="O29" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
@@ -2447,59 +2447,59 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>02:21</t>
+          <t>04:19</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B30" t="n">
-        <v>854393</v>
+        <v>854612</v>
       </c>
       <c r="C30" t="n">
-        <v>250300</v>
+        <v>461544</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NOTA PROMISSORIA TIL 50FLS</t>
+          <t>BISC NESTLE 60GR COOKIES CLASSIC BAUN</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2793033804</v>
+        <v>5648006579</v>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>84,21</t>
+          <t>135,44</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="I30" t="n">
-        <v>50</v>
+        <v>104</v>
       </c>
       <c r="J30" t="n">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="K30" t="n">
         <v>2</v>
       </c>
       <c r="L30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M30" t="n">
-        <v>56.14</v>
+        <v>135.44</v>
       </c>
       <c r="N30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O30" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
@@ -2507,137 +2507,137 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>180809</v>
+        <v>122537</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>GABRIELA DE SOUSA BEZERRA</t>
+          <t>YAGO RODRIGUES DA SILVA</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>02:33</t>
+          <t>04:06</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B31" t="n">
-        <v>854469</v>
+        <v>854625</v>
       </c>
       <c r="C31" t="n">
-        <v>465489</v>
+        <v>454948</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>CANETA ESF CIS SPIRO SORT 24UN</t>
+          <t>KIMELEKA ACRILEX 180GR SORTIDA</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>3417051244</v>
+        <v>4132035144</v>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>88,46</t>
+          <t>75,91</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I31" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J31" t="n">
-        <v>201</v>
+        <v>102</v>
       </c>
       <c r="K31" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
-        <v>88.45999999999999</v>
+        <v>75.91</v>
       </c>
       <c r="N31" t="n">
+        <v>4</v>
+      </c>
+      <c r="O31" t="n">
         <v>22</v>
       </c>
-      <c r="O31" t="n">
-        <v>20</v>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>QUANTIDADE INFERIOR DA OS</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>181203</v>
+        <v>122537</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>JANAINA SOUSA PAIXAO</t>
+          <t>YAGO RODRIGUES DA SILVA</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>22:20</t>
+          <t>04:22</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B32" t="n">
-        <v>854404</v>
+        <v>854673</v>
       </c>
       <c r="C32" t="n">
-        <v>470878</v>
+        <v>468083</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>FITA ADES EMPAC TEK BOND TRANSP 48MMX40M</t>
+          <t>CREME DE AVELA NUTELLA FERRERO 350GR RTD</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5649005314</v>
+        <v>2424052389</v>
       </c>
       <c r="F32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>22,68</t>
+          <t>1.259,40</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>28</v>
+        <v>200</v>
       </c>
       <c r="I32" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J32" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K32" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>22.68</v>
+        <v>1259.4</v>
       </c>
       <c r="N32" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O32" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
@@ -2645,1672 +2645,16 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>180809</v>
+        <v>180185</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>GABRIELA DE SOUSA BEZERRA</t>
+          <t>ALEANDRA TRINDADE SOUSA</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>02:32</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>46133</v>
-      </c>
-      <c r="B33" t="n">
-        <v>854398</v>
-      </c>
-      <c r="C33" t="n">
-        <v>476051</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>PASTA ELASTICO PLASCONY 20MM AZUL</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>1664041395</v>
-      </c>
-      <c r="F33" t="n">
-        <v>1</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>21,57</t>
-        </is>
-      </c>
-      <c r="H33" t="n">
-        <v>30</v>
-      </c>
-      <c r="I33" t="n">
-        <v>33</v>
-      </c>
-      <c r="J33" t="n">
-        <v>204</v>
-      </c>
-      <c r="K33" t="n">
-        <v>1</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1</v>
-      </c>
-      <c r="M33" t="n">
-        <v>21.57</v>
-      </c>
-      <c r="N33" t="n">
-        <v>3</v>
-      </c>
-      <c r="O33" t="n">
-        <v>28</v>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>QUANTIDADE INFERIOR DA OS</t>
-        </is>
-      </c>
-      <c r="Q33" t="n">
-        <v>122537</v>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>YAGO RODRIGUES DA SILVA</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>03:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>46133</v>
-      </c>
-      <c r="B34" t="n">
-        <v>854403</v>
-      </c>
-      <c r="C34" t="n">
-        <v>459840</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>AMENDOIM DORI 320GR LASCA DE ALHO</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>5905000339</v>
-      </c>
-      <c r="F34" t="n">
-        <v>3</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>31,50</t>
-        </is>
-      </c>
-      <c r="H34" t="n">
-        <v>11</v>
-      </c>
-      <c r="I34" t="n">
-        <v>94</v>
-      </c>
-      <c r="J34" t="n">
-        <v>202</v>
-      </c>
-      <c r="K34" t="n">
-        <v>2</v>
-      </c>
-      <c r="L34" t="n">
-        <v>1</v>
-      </c>
-      <c r="M34" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="N34" t="n">
-        <v>4</v>
-      </c>
-      <c r="O34" t="n">
-        <v>33</v>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>QUANTIDADE INFERIOR DA OS</t>
-        </is>
-      </c>
-      <c r="Q34" t="n">
-        <v>122537</v>
-      </c>
-      <c r="R34" t="inlineStr">
-        <is>
-          <t>YAGO RODRIGUES DA SILVA</t>
-        </is>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>04:33</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>46133</v>
-      </c>
-      <c r="B35" t="n">
-        <v>854489</v>
-      </c>
-      <c r="C35" t="n">
-        <v>476790</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>CHOC FERRERO KINDER BUENO DARK 43GR T2</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>1826041482</v>
-      </c>
-      <c r="F35" t="n">
-        <v>2</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>329,38</t>
-        </is>
-      </c>
-      <c r="H35" t="n">
-        <v>60</v>
-      </c>
-      <c r="I35" t="n">
-        <v>1</v>
-      </c>
-      <c r="J35" t="n">
-        <v>723</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" t="n">
-        <v>2</v>
-      </c>
-      <c r="M35" t="n">
-        <v>329.38</v>
-      </c>
-      <c r="N35" t="n">
-        <v>21</v>
-      </c>
-      <c r="O35" t="n">
-        <v>51</v>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>QUANTIDADE INFERIOR DA OS</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>122537</v>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>YAGO RODRIGUES DA SILVA</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>21:51</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>46133</v>
-      </c>
-      <c r="B36" t="n">
-        <v>854472</v>
-      </c>
-      <c r="C36" t="n">
-        <v>465489</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>CANETA ESF CIS SPIRO SORT 24UN</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>5968000257</v>
-      </c>
-      <c r="F36" t="n">
-        <v>2</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>96,62</t>
-        </is>
-      </c>
-      <c r="H36" t="n">
-        <v>32</v>
-      </c>
-      <c r="I36" t="n">
-        <v>8</v>
-      </c>
-      <c r="J36" t="n">
-        <v>201</v>
-      </c>
-      <c r="K36" t="n">
-        <v>42</v>
-      </c>
-      <c r="L36" t="n">
-        <v>1</v>
-      </c>
-      <c r="M36" t="n">
-        <v>48.31</v>
-      </c>
-      <c r="N36" t="n">
-        <v>22</v>
-      </c>
-      <c r="O36" t="n">
-        <v>3</v>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>QUANTIDADE INFERIOR DA OS</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>181203</v>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>JANAINA SOUSA PAIXAO</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>22:03</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>46133</v>
-      </c>
-      <c r="B37" t="n">
-        <v>854472</v>
-      </c>
-      <c r="C37" t="n">
-        <v>465489</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>CANETA ESF CIS SPIRO SORT 24UN</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>5968000260</v>
-      </c>
-      <c r="F37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>46,08</t>
-        </is>
-      </c>
-      <c r="H37" t="n">
-        <v>32</v>
-      </c>
-      <c r="I37" t="n">
-        <v>8</v>
-      </c>
-      <c r="J37" t="n">
-        <v>201</v>
-      </c>
-      <c r="K37" t="n">
-        <v>42</v>
-      </c>
-      <c r="L37" t="n">
-        <v>1</v>
-      </c>
-      <c r="M37" t="n">
-        <v>46.08</v>
-      </c>
-      <c r="N37" t="n">
-        <v>22</v>
-      </c>
-      <c r="O37" t="n">
-        <v>3</v>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>QUANTIDADE INFERIOR DA OS</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>181203</v>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>JANAINA SOUSA PAIXAO</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>22:03</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>46133</v>
-      </c>
-      <c r="B38" t="n">
-        <v>854453</v>
-      </c>
-      <c r="C38" t="n">
-        <v>420215</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>BALAO SAO ROQUE 7 ROSA TUTI FRUTI 50UN</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>3756059667</v>
-      </c>
-      <c r="F38" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>77,13</t>
-        </is>
-      </c>
-      <c r="H38" t="n">
-        <v>18</v>
-      </c>
-      <c r="I38" t="n">
-        <v>29</v>
-      </c>
-      <c r="J38" t="n">
-        <v>102</v>
-      </c>
-      <c r="K38" t="n">
-        <v>3</v>
-      </c>
-      <c r="L38" t="n">
-        <v>1</v>
-      </c>
-      <c r="M38" t="n">
-        <v>77.13</v>
-      </c>
-      <c r="N38" t="n">
-        <v>21</v>
-      </c>
-      <c r="O38" t="n">
-        <v>47</v>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>QUANTIDADE INFERIOR DA OS</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>122537</v>
-      </c>
-      <c r="R38" t="inlineStr">
-        <is>
-          <t>YAGO RODRIGUES DA SILVA</t>
-        </is>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>21:47</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>46133</v>
-      </c>
-      <c r="B39" t="n">
-        <v>854474</v>
-      </c>
-      <c r="C39" t="n">
-        <v>472113</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>LUVA VABENE NITRILICA PRETA M 100UN</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>5141006234</v>
-      </c>
-      <c r="F39" t="n">
-        <v>2</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>46,76</t>
-        </is>
-      </c>
-      <c r="H39" t="n">
-        <v>16</v>
-      </c>
-      <c r="I39" t="n">
-        <v>61</v>
-      </c>
-      <c r="J39" t="n">
-        <v>204</v>
-      </c>
-      <c r="K39" t="n">
-        <v>3</v>
-      </c>
-      <c r="L39" t="n">
-        <v>1</v>
-      </c>
-      <c r="M39" t="n">
-        <v>23.38</v>
-      </c>
-      <c r="N39" t="n">
-        <v>23</v>
-      </c>
-      <c r="O39" t="n">
-        <v>8</v>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>QUANTIDADE INFERIOR DA OS</t>
-        </is>
-      </c>
-      <c r="Q39" t="n">
-        <v>122537</v>
-      </c>
-      <c r="R39" t="inlineStr">
-        <is>
-          <t>YAGO RODRIGUES DA SILVA</t>
-        </is>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>23:08</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>46133</v>
-      </c>
-      <c r="B40" t="n">
-        <v>854439</v>
-      </c>
-      <c r="C40" t="n">
-        <v>441861</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>MANGUEIRA BARIFLEX TRANC VERDE 30MT</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>1070123305</v>
-      </c>
-      <c r="F40" t="n">
-        <v>2</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>109,08</t>
-        </is>
-      </c>
-      <c r="H40" t="n">
-        <v>25</v>
-      </c>
-      <c r="I40" t="n">
-        <v>29</v>
-      </c>
-      <c r="J40" t="n">
-        <v>102</v>
-      </c>
-      <c r="K40" t="n">
-        <v>1</v>
-      </c>
-      <c r="L40" t="n">
-        <v>1</v>
-      </c>
-      <c r="M40" t="n">
-        <v>54.54</v>
-      </c>
-      <c r="N40" t="n">
-        <v>22</v>
-      </c>
-      <c r="O40" t="n">
-        <v>22</v>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>QUANTIDADE INFERIOR DA OS</t>
-        </is>
-      </c>
-      <c r="Q40" t="n">
-        <v>122537</v>
-      </c>
-      <c r="R40" t="inlineStr">
-        <is>
-          <t>YAGO RODRIGUES DA SILVA</t>
-        </is>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>22:22</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>46133</v>
-      </c>
-      <c r="B41" t="n">
-        <v>854370</v>
-      </c>
-      <c r="C41" t="n">
-        <v>431553</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>DOCE LEITE ITAMBE LATA 800GR</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>4988051966</v>
-      </c>
-      <c r="F41" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>378,73</t>
-        </is>
-      </c>
-      <c r="H41" t="n">
-        <v>6</v>
-      </c>
-      <c r="I41" t="n">
-        <v>71</v>
-      </c>
-      <c r="J41" t="n">
-        <v>101</v>
-      </c>
-      <c r="K41" t="n">
-        <v>11</v>
-      </c>
-      <c r="L41" t="n">
-        <v>1</v>
-      </c>
-      <c r="M41" t="n">
-        <v>378.73</v>
-      </c>
-      <c r="N41" t="n">
-        <v>3</v>
-      </c>
-      <c r="O41" t="n">
-        <v>28</v>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>QUANTIDADE INFERIOR DA OS</t>
-        </is>
-      </c>
-      <c r="Q41" t="n">
-        <v>122537</v>
-      </c>
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>YAGO RODRIGUES DA SILVA</t>
-        </is>
-      </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>03:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n">
-        <v>46133</v>
-      </c>
-      <c r="B42" t="n">
-        <v>854503</v>
-      </c>
-      <c r="C42" t="n">
-        <v>472236</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>SAND HAV BRASIL  LOGO AMARELO VERDE 37/8</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>5781001649</v>
-      </c>
-      <c r="F42" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>41,04</t>
-        </is>
-      </c>
-      <c r="H42" t="n">
-        <v>36</v>
-      </c>
-      <c r="I42" t="n">
-        <v>20</v>
-      </c>
-      <c r="J42" t="n">
-        <v>204</v>
-      </c>
-      <c r="K42" t="n">
-        <v>1</v>
-      </c>
-      <c r="L42" t="n">
-        <v>1</v>
-      </c>
-      <c r="M42" t="n">
-        <v>41.04</v>
-      </c>
-      <c r="N42" t="n">
-        <v>22</v>
-      </c>
-      <c r="O42" t="n">
-        <v>11</v>
-      </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>QUANTIDADE INFERIOR DA OS</t>
-        </is>
-      </c>
-      <c r="Q42" t="n">
-        <v>180185</v>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>ALEANDRA TRINDADE SOUSA</t>
-        </is>
-      </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>22:11</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n">
-        <v>46133</v>
-      </c>
-      <c r="B43" t="n">
-        <v>854378</v>
-      </c>
-      <c r="C43" t="n">
-        <v>472238</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>SAND HAV BRASIL  LOGO AMARELO VERDE 41/2</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>4126012094</v>
-      </c>
-      <c r="F43" t="n">
-        <v>2</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>88,32</t>
-        </is>
-      </c>
-      <c r="H43" t="n">
-        <v>36</v>
-      </c>
-      <c r="I43" t="n">
-        <v>13</v>
-      </c>
-      <c r="J43" t="n">
-        <v>102</v>
-      </c>
-      <c r="K43" t="n">
-        <v>24</v>
-      </c>
-      <c r="L43" t="n">
-        <v>2</v>
-      </c>
-      <c r="M43" t="n">
-        <v>88.31999999999999</v>
-      </c>
-      <c r="N43" t="n">
-        <v>10</v>
-      </c>
-      <c r="O43" t="n">
-        <v>2</v>
-      </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>QUANTIDADE INFERIOR DA OS</t>
-        </is>
-      </c>
-      <c r="Q43" t="n">
-        <v>100715</v>
-      </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>ANTONIA FRANÇA NASCIMENTO CAMPOS</t>
-        </is>
-      </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>10:02</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>46133</v>
-      </c>
-      <c r="B44" t="n">
-        <v>854378</v>
-      </c>
-      <c r="C44" t="n">
-        <v>472237</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>SAND HAV BRASIL  LOGO AMARELO VERDE 39/0</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>4126012094</v>
-      </c>
-      <c r="F44" t="n">
-        <v>2</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>88,32</t>
-        </is>
-      </c>
-      <c r="H44" t="n">
-        <v>34</v>
-      </c>
-      <c r="I44" t="n">
-        <v>14</v>
-      </c>
-      <c r="J44" t="n">
-        <v>202</v>
-      </c>
-      <c r="K44" t="n">
-        <v>24</v>
-      </c>
-      <c r="L44" t="n">
-        <v>2</v>
-      </c>
-      <c r="M44" t="n">
-        <v>88.31999999999999</v>
-      </c>
-      <c r="N44" t="n">
-        <v>9</v>
-      </c>
-      <c r="O44" t="n">
-        <v>7</v>
-      </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>QUANTIDADE INFERIOR DA OS</t>
-        </is>
-      </c>
-      <c r="Q44" t="n">
-        <v>181227</v>
-      </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>KELIANE DE CARVALHO SOUSA FERREIRA</t>
-        </is>
-      </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>09:07</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="n">
-        <v>46133</v>
-      </c>
-      <c r="B45" t="n">
-        <v>854448</v>
-      </c>
-      <c r="C45" t="n">
-        <v>472238</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>SAND HAV BRASIL  LOGO AMARELO VERDE 41/2</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>2828054732</v>
-      </c>
-      <c r="F45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>40,19</t>
-        </is>
-      </c>
-      <c r="H45" t="n">
-        <v>36</v>
-      </c>
-      <c r="I45" t="n">
-        <v>13</v>
-      </c>
-      <c r="J45" t="n">
-        <v>102</v>
-      </c>
-      <c r="K45" t="n">
-        <v>24</v>
-      </c>
-      <c r="L45" t="n">
-        <v>1</v>
-      </c>
-      <c r="M45" t="n">
-        <v>40.19</v>
-      </c>
-      <c r="N45" t="n">
-        <v>21</v>
-      </c>
-      <c r="O45" t="n">
-        <v>28</v>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>QUANTIDADE INFERIOR DA OS</t>
-        </is>
-      </c>
-      <c r="Q45" t="n">
-        <v>122618</v>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>WEBERT JOSE DA SILVA</t>
-        </is>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>21:28</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="n">
-        <v>46133</v>
-      </c>
-      <c r="B46" t="n">
-        <v>854353</v>
-      </c>
-      <c r="C46" t="n">
-        <v>472237</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>SAND HAV BRASIL  LOGO AMARELO VERDE 39/0</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>3684022632</v>
-      </c>
-      <c r="F46" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>39,92</t>
-        </is>
-      </c>
-      <c r="H46" t="n">
-        <v>34</v>
-      </c>
-      <c r="I46" t="n">
-        <v>14</v>
-      </c>
-      <c r="J46" t="n">
-        <v>202</v>
-      </c>
-      <c r="K46" t="n">
-        <v>24</v>
-      </c>
-      <c r="L46" t="n">
-        <v>1</v>
-      </c>
-      <c r="M46" t="n">
-        <v>39.92</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>45</v>
-      </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>QUANTIDADE INFERIOR DA OS</t>
-        </is>
-      </c>
-      <c r="Q46" t="n">
-        <v>181349</v>
-      </c>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>KASSIANE SOUZA SEIXAS</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>00:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="n">
-        <v>46133</v>
-      </c>
-      <c r="B47" t="n">
-        <v>854440</v>
-      </c>
-      <c r="C47" t="n">
-        <v>472238</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>SAND HAV BRASIL  LOGO AMARELO VERDE 41/2</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>4196028577</v>
-      </c>
-      <c r="F47" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>40,48</t>
-        </is>
-      </c>
-      <c r="H47" t="n">
-        <v>36</v>
-      </c>
-      <c r="I47" t="n">
-        <v>13</v>
-      </c>
-      <c r="J47" t="n">
-        <v>102</v>
-      </c>
-      <c r="K47" t="n">
-        <v>24</v>
-      </c>
-      <c r="L47" t="n">
-        <v>1</v>
-      </c>
-      <c r="M47" t="n">
-        <v>40.48</v>
-      </c>
-      <c r="N47" t="n">
-        <v>23</v>
-      </c>
-      <c r="O47" t="n">
-        <v>36</v>
-      </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>QUANTIDADE INFERIOR DA OS</t>
-        </is>
-      </c>
-      <c r="Q47" t="n">
-        <v>122574</v>
-      </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>LEILIENE DO BOM PARTO SOUSA COSTA</t>
-        </is>
-      </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>23:36</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="n">
-        <v>46133</v>
-      </c>
-      <c r="B48" t="n">
-        <v>854448</v>
-      </c>
-      <c r="C48" t="n">
-        <v>472237</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>SAND HAV BRASIL  LOGO AMARELO VERDE 39/0</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>2828054732</v>
-      </c>
-      <c r="F48" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>40,19</t>
-        </is>
-      </c>
-      <c r="H48" t="n">
-        <v>34</v>
-      </c>
-      <c r="I48" t="n">
-        <v>14</v>
-      </c>
-      <c r="J48" t="n">
-        <v>202</v>
-      </c>
-      <c r="K48" t="n">
-        <v>24</v>
-      </c>
-      <c r="L48" t="n">
-        <v>1</v>
-      </c>
-      <c r="M48" t="n">
-        <v>40.19</v>
-      </c>
-      <c r="N48" t="n">
-        <v>21</v>
-      </c>
-      <c r="O48" t="n">
-        <v>27</v>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>QUANTIDADE INFERIOR DA OS</t>
-        </is>
-      </c>
-      <c r="Q48" t="n">
-        <v>122618</v>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>WEBERT JOSE DA SILVA</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>21:27</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="n">
-        <v>46133</v>
-      </c>
-      <c r="B49" t="n">
-        <v>854440</v>
-      </c>
-      <c r="C49" t="n">
-        <v>472237</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>SAND HAV BRASIL  LOGO AMARELO VERDE 39/0</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>4196028577</v>
-      </c>
-      <c r="F49" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>40,48</t>
-        </is>
-      </c>
-      <c r="H49" t="n">
-        <v>34</v>
-      </c>
-      <c r="I49" t="n">
-        <v>14</v>
-      </c>
-      <c r="J49" t="n">
-        <v>202</v>
-      </c>
-      <c r="K49" t="n">
-        <v>24</v>
-      </c>
-      <c r="L49" t="n">
-        <v>1</v>
-      </c>
-      <c r="M49" t="n">
-        <v>40.48</v>
-      </c>
-      <c r="N49" t="n">
-        <v>22</v>
-      </c>
-      <c r="O49" t="n">
-        <v>30</v>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>QUANTIDADE INFERIOR DA OS</t>
-        </is>
-      </c>
-      <c r="Q49" t="n">
-        <v>122574</v>
-      </c>
-      <c r="R49" t="inlineStr">
-        <is>
-          <t>LEILIENE DO BOM PARTO SOUSA COSTA</t>
-        </is>
-      </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="n">
-        <v>46133</v>
-      </c>
-      <c r="B50" t="n">
-        <v>854469</v>
-      </c>
-      <c r="C50" t="n">
-        <v>469865</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>REPELENTE OFF SPRAY 170ML FAMILY</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>3417051242</v>
-      </c>
-      <c r="F50" t="n">
-        <v>10</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>199,60</t>
-        </is>
-      </c>
-      <c r="H50" t="n">
-        <v>31</v>
-      </c>
-      <c r="I50" t="n">
-        <v>4</v>
-      </c>
-      <c r="J50" t="n">
-        <v>1.001</v>
-      </c>
-      <c r="K50" t="n">
-        <v>11</v>
-      </c>
-      <c r="L50" t="n">
-        <v>10</v>
-      </c>
-      <c r="M50" t="n">
-        <v>199.6</v>
-      </c>
-      <c r="N50" t="n">
-        <v>22</v>
-      </c>
-      <c r="O50" t="n">
-        <v>44</v>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>QUANTIDADE INFERIOR DA OS</t>
-        </is>
-      </c>
-      <c r="Q50" t="n">
-        <v>181332</v>
-      </c>
-      <c r="R50" t="inlineStr">
-        <is>
-          <t>NAYARA PEREIRA ROSA</t>
-        </is>
-      </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>22:44</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="n">
-        <v>46133</v>
-      </c>
-      <c r="B51" t="n">
-        <v>854459</v>
-      </c>
-      <c r="C51" t="n">
-        <v>461740</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>BISC MARIL TORTINHA 300GR CHOCOLATE</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>3687032448</v>
-      </c>
-      <c r="F51" t="n">
-        <v>1</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>149,63</t>
-        </is>
-      </c>
-      <c r="H51" t="n">
-        <v>2</v>
-      </c>
-      <c r="I51" t="n">
-        <v>16</v>
-      </c>
-      <c r="J51" t="n">
-        <v>101</v>
-      </c>
-      <c r="K51" t="n">
-        <v>41</v>
-      </c>
-      <c r="L51" t="n">
-        <v>1</v>
-      </c>
-      <c r="M51" t="n">
-        <v>149.63</v>
-      </c>
-      <c r="N51" t="n">
-        <v>21</v>
-      </c>
-      <c r="O51" t="n">
-        <v>2</v>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>QUANTIDADE INFERIOR DA OS</t>
-        </is>
-      </c>
-      <c r="Q51" t="n">
-        <v>122537</v>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>YAGO RODRIGUES DA SILVA</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>21:02</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="n">
-        <v>46133</v>
-      </c>
-      <c r="B52" t="n">
-        <v>854404</v>
-      </c>
-      <c r="C52" t="n">
-        <v>469498</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>BISC MARIL LEV 110GR MAG TOAST INTEGRAL</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>5905000348</v>
-      </c>
-      <c r="F52" t="n">
-        <v>2</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>10,60</t>
-        </is>
-      </c>
-      <c r="H52" t="n">
-        <v>12</v>
-      </c>
-      <c r="I52" t="n">
-        <v>31</v>
-      </c>
-      <c r="J52" t="n">
-        <v>101</v>
-      </c>
-      <c r="K52" t="n">
-        <v>12</v>
-      </c>
-      <c r="L52" t="n">
-        <v>2</v>
-      </c>
-      <c r="M52" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="N52" t="n">
-        <v>3</v>
-      </c>
-      <c r="O52" t="n">
-        <v>37</v>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>QUANTIDADE INFERIOR DA OS</t>
-        </is>
-      </c>
-      <c r="Q52" t="n">
-        <v>122537</v>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>YAGO RODRIGUES DA SILVA</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>03:37</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="n">
-        <v>46133</v>
-      </c>
-      <c r="B53" t="n">
-        <v>854453</v>
-      </c>
-      <c r="C53" t="n">
-        <v>454255</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>AMAC COMFORT 500ML CONC C ESSENC AZ</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>1836021975</v>
-      </c>
-      <c r="F53" t="n">
-        <v>2</v>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>20,72</t>
-        </is>
-      </c>
-      <c r="H53" t="n">
-        <v>26</v>
-      </c>
-      <c r="I53" t="n">
-        <v>17</v>
-      </c>
-      <c r="J53" t="n">
-        <v>101</v>
-      </c>
-      <c r="K53" t="n">
-        <v>5</v>
-      </c>
-      <c r="L53" t="n">
-        <v>2</v>
-      </c>
-      <c r="M53" t="n">
-        <v>20.72</v>
-      </c>
-      <c r="N53" t="n">
-        <v>21</v>
-      </c>
-      <c r="O53" t="n">
-        <v>49</v>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>QUANTIDADE INFERIOR DA OS</t>
-        </is>
-      </c>
-      <c r="Q53" t="n">
-        <v>122537</v>
-      </c>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>YAGO RODRIGUES DA SILVA</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>21:49</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="n">
-        <v>46133</v>
-      </c>
-      <c r="B54" t="n">
-        <v>854402</v>
-      </c>
-      <c r="C54" t="n">
-        <v>461857</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>ALGODAO COTTONBABY BOLA 50GR 30UN</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>2301019785</v>
-      </c>
-      <c r="F54" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>4,15</t>
-        </is>
-      </c>
-      <c r="H54" t="n">
-        <v>18</v>
-      </c>
-      <c r="I54" t="n">
-        <v>45</v>
-      </c>
-      <c r="J54" t="n">
-        <v>102</v>
-      </c>
-      <c r="K54" t="n">
-        <v>1</v>
-      </c>
-      <c r="L54" t="n">
-        <v>1</v>
-      </c>
-      <c r="M54" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="N54" t="n">
-        <v>2</v>
-      </c>
-      <c r="O54" t="n">
-        <v>21</v>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>QUANTIDADE INFERIOR DA OS</t>
-        </is>
-      </c>
-      <c r="Q54" t="n">
-        <v>122537</v>
-      </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>YAGO RODRIGUES DA SILVA</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>02:21</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="n">
-        <v>46134</v>
-      </c>
-      <c r="B55" t="n">
-        <v>854469</v>
-      </c>
-      <c r="C55" t="n">
-        <v>455159</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>AMENDOIM BONISSIMO 1,010KG TORRADO GRANU</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>5811001424</v>
-      </c>
-      <c r="F55" t="n">
-        <v>4</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>108,48</t>
-        </is>
-      </c>
-      <c r="H55" t="n">
-        <v>12</v>
-      </c>
-      <c r="I55" t="n">
-        <v>89</v>
-      </c>
-      <c r="J55" t="n">
-        <v>102</v>
-      </c>
-      <c r="K55" t="n">
-        <v>19</v>
-      </c>
-      <c r="L55" t="n">
-        <v>3</v>
-      </c>
-      <c r="M55" t="n">
-        <v>81.36</v>
-      </c>
-      <c r="N55" t="n">
-        <v>2</v>
-      </c>
-      <c r="O55" t="n">
-        <v>11</v>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>QUANTIDADE INFERIOR DA OS</t>
-        </is>
-      </c>
-      <c r="Q55" t="n">
-        <v>122537</v>
-      </c>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>YAGO RODRIGUES DA SILVA</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>02:11</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="n">
-        <v>46134</v>
-      </c>
-      <c r="B56" t="n">
-        <v>854502</v>
-      </c>
-      <c r="C56" t="n">
-        <v>420215</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>BALAO SAO ROQUE 7 ROSA TUTI FRUTI 50UN</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>5157004873</v>
-      </c>
-      <c r="F56" t="n">
-        <v>1</v>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>77,13</t>
-        </is>
-      </c>
-      <c r="H56" t="n">
-        <v>18</v>
-      </c>
-      <c r="I56" t="n">
-        <v>29</v>
-      </c>
-      <c r="J56" t="n">
-        <v>102</v>
-      </c>
-      <c r="K56" t="n">
-        <v>3</v>
-      </c>
-      <c r="L56" t="n">
-        <v>1</v>
-      </c>
-      <c r="M56" t="n">
-        <v>77.13</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" t="n">
-        <v>50</v>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>QUANTIDADE INFERIOR DA OS</t>
-        </is>
-      </c>
-      <c r="Q56" t="n">
-        <v>122537</v>
-      </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>YAGO RODRIGUES DA SILVA</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>00:50</t>
+          <t>04:48</t>
         </is>
       </c>
     </row>
@@ -4325,7 +2669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4427,53 +2771,53 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B2" t="n">
-        <v>854378</v>
+        <v>854546</v>
       </c>
       <c r="C2" t="n">
-        <v>472238</v>
+        <v>476816</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>SAND HAV BRASIL  LOGO AMARELO VERDE 41/2</t>
+          <t>PAO BISNAGUINHA VISCONTI 240GR</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4126012094</v>
+        <v>2371039072</v>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>88,32</t>
+          <t>141,12</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="J2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K2" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>88.31999999999999</v>
+        <v>35.28</v>
       </c>
       <c r="N2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="O2" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -4481,85 +2825,637 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>100715</v>
+        <v>180101</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>ANTONIA FRANÇA NASCIMENTO CAMPOS</t>
+          <t>CARLOS ALBERTO SANTOS DA SILVA FILHO</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>16:43</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B3" t="n">
-        <v>854378</v>
+        <v>854509</v>
       </c>
       <c r="C3" t="n">
-        <v>472237</v>
+        <v>470842</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SAND HAV BRASIL  LOGO AMARELO VERDE 39/0</t>
+          <t>ACHOC NESCAU 730GR SACHET</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4126012094</v>
+        <v>99046723</v>
       </c>
       <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>21,18</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>10</v>
+      </c>
+      <c r="I3" t="n">
+        <v>87</v>
+      </c>
+      <c r="J3" t="n">
+        <v>102</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>21.18</v>
+      </c>
+      <c r="N3" t="n">
+        <v>11</v>
+      </c>
+      <c r="O3" t="n">
+        <v>15</v>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>QUANTIDADE INFERIOR DA OS</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>180101</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO SANTOS DA SILVA FILHO</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>11:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B4" t="n">
+        <v>854546</v>
+      </c>
+      <c r="C4" t="n">
+        <v>427994</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>AZEITE E VIRG PORT ANDORINHA 500ML VIDRO</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2371039083</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>83,91</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>12</v>
+      </c>
+      <c r="I4" t="n">
+        <v>6</v>
+      </c>
+      <c r="J4" t="n">
+        <v>101</v>
+      </c>
+      <c r="K4" t="n">
+        <v>34</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>83.91</v>
+      </c>
+      <c r="N4" t="n">
+        <v>15</v>
+      </c>
+      <c r="O4" t="n">
+        <v>51</v>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>QUANTIDADE INFERIOR DA OS</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>180101</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO SANTOS DA SILVA FILHO</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B5" t="n">
+        <v>854435</v>
+      </c>
+      <c r="C5" t="n">
+        <v>427994</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>AZEITE E VIRG PORT ANDORINHA 500ML VIDRO</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>7153000103</v>
+      </c>
+      <c r="F5" t="n">
+        <v>480</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>12.739,20</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>101</v>
+      </c>
+      <c r="K5" t="n">
+        <v>34</v>
+      </c>
+      <c r="L5" t="n">
+        <v>252</v>
+      </c>
+      <c r="M5" t="n">
+        <v>6688.08</v>
+      </c>
+      <c r="N5" t="n">
+        <v>11</v>
+      </c>
+      <c r="O5" t="n">
+        <v>12</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>QUANTIDADE INFERIOR DA OS</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>180101</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO SANTOS DA SILVA FILHO</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B6" t="n">
+        <v>854551</v>
+      </c>
+      <c r="C6" t="n">
+        <v>463671</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>SABAO PO ASSIM 800GR BICARBONATO</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2557057589</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>144,21</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>14</v>
+      </c>
+      <c r="I6" t="n">
+        <v>35</v>
+      </c>
+      <c r="J6" t="n">
+        <v>101</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>144.21</v>
+      </c>
+      <c r="N6" t="n">
+        <v>17</v>
+      </c>
+      <c r="O6" t="n">
         <v>2</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>88,32</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>34</v>
-      </c>
-      <c r="I3" t="n">
-        <v>14</v>
-      </c>
-      <c r="J3" t="n">
-        <v>202</v>
-      </c>
-      <c r="K3" t="n">
-        <v>24</v>
-      </c>
-      <c r="L3" t="n">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>QUANTIDADE INFERIOR DA OS</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>180101</v>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO SANTOS DA SILVA FILHO</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B7" t="n">
+        <v>854555</v>
+      </c>
+      <c r="C7" t="n">
+        <v>465372</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CHOC FERRERO KINDER BUENO WHITE 39GR T2</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>7154000035</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>81,89</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>70</v>
+      </c>
+      <c r="I7" t="n">
+        <v>6</v>
+      </c>
+      <c r="J7" t="n">
+        <v>273</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>81.89</v>
+      </c>
+      <c r="N7" t="n">
+        <v>17</v>
+      </c>
+      <c r="O7" t="n">
+        <v>25</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>QUANTIDADE INFERIOR DA OS</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>180101</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO SANTOS DA SILVA FILHO</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B8" t="n">
+        <v>854478</v>
+      </c>
+      <c r="C8" t="n">
+        <v>423385</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>COPO DESC COPOBRAS 200ML TRA 100UN PS</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5055005120</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>99,79</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>17</v>
+      </c>
+      <c r="I8" t="n">
+        <v>20</v>
+      </c>
+      <c r="J8" t="n">
+        <v>101</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>99.79000000000001</v>
+      </c>
+      <c r="N8" t="n">
+        <v>10</v>
+      </c>
+      <c r="O8" t="n">
+        <v>32</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>QUANTIDADE INFERIOR DA OS</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>180101</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO SANTOS DA SILVA FILHO</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B9" t="n">
+        <v>854496</v>
+      </c>
+      <c r="C9" t="n">
+        <v>420215</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>BALAO SAO ROQUE 7 ROSA TUTI FRUTI 50UN</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3965027900</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>83,64</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>18</v>
+      </c>
+      <c r="I9" t="n">
+        <v>29</v>
+      </c>
+      <c r="J9" t="n">
+        <v>102</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>83.64</v>
+      </c>
+      <c r="N9" t="n">
+        <v>10</v>
+      </c>
+      <c r="O9" t="n">
+        <v>47</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>QUANTIDADE INFERIOR DA OS</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>180101</v>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO SANTOS DA SILVA FILHO</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B10" t="n">
+        <v>854551</v>
+      </c>
+      <c r="C10" t="n">
+        <v>448771</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CREME TRAT SKALA 1KG JABORANDI</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5049020306</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>7,84</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>60</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>403</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="N10" t="n">
+        <v>13</v>
+      </c>
+      <c r="O10" t="n">
+        <v>45</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>QUANTIDADE INFERIOR DA OS</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>180101</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO SANTOS DA SILVA FILHO</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B11" t="n">
+        <v>854480</v>
+      </c>
+      <c r="C11" t="n">
+        <v>476941</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CHOCOLATE NESTLE PRESTIGIO 33GR FUT VERM</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>3266031639</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>83,04</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>10</v>
+      </c>
+      <c r="I11" t="n">
+        <v>103</v>
+      </c>
+      <c r="J11" t="n">
+        <v>101</v>
+      </c>
+      <c r="K11" t="n">
         <v>2</v>
       </c>
-      <c r="M3" t="n">
-        <v>88.31999999999999</v>
-      </c>
-      <c r="N3" t="n">
-        <v>9</v>
-      </c>
-      <c r="O3" t="n">
-        <v>7</v>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>QUANTIDADE INFERIOR DA OS</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>181227</v>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>KELIANE DE CARVALHO SOUSA FERREIRA</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>09:07</t>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>83.04000000000001</v>
+      </c>
+      <c r="N11" t="n">
+        <v>11</v>
+      </c>
+      <c r="O11" t="n">
+        <v>56</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>QUANTIDADE INFERIOR DA OS</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>180101</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>CARLOS ALBERTO SANTOS DA SILVA FILHO</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>11:56</t>
         </is>
       </c>
     </row>
@@ -4681,53 +3577,53 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B2" t="n">
-        <v>854477</v>
+        <v>854587</v>
       </c>
       <c r="C2" t="n">
-        <v>465489</v>
+        <v>476941</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CANETA ESF CIS SPIRO SORT 24UN</t>
+          <t>CHOCOLATE NESTLE PRESTIGIO 33GR FUT VERM</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5875000562</v>
+        <v>5097012473</v>
       </c>
       <c r="F2" t="n">
         <v>1</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>42,60</t>
+          <t>94,94</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>103</v>
       </c>
       <c r="J2" t="n">
-        <v>201</v>
+        <v>101</v>
       </c>
       <c r="K2" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
         <v>1</v>
       </c>
       <c r="M2" t="n">
-        <v>42.6</v>
+        <v>94.94</v>
       </c>
       <c r="N2" t="n">
         <v>22</v>
       </c>
       <c r="O2" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -4735,71 +3631,71 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>181203</v>
+        <v>180121</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>JANAINA SOUSA PAIXAO</t>
+          <t>TAINA MEDEIROS RIBEIRO</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>22:13</t>
+          <t>22:17</t>
         </is>
       </c>
       <c r="T2" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B3" t="n">
-        <v>854476</v>
+        <v>854555</v>
       </c>
       <c r="C3" t="n">
-        <v>468667</v>
+        <v>449719</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PACOCA ROLHA EMB MORENINHA DO RIO 300GR</t>
+          <t>PALMITO PALMEIRAL ACAI INTEIRO 1,8KG</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5282003968</v>
+        <v>4591009852</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>8,11</t>
+          <t>425,72</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I3" t="n">
-        <v>46</v>
+        <v>85</v>
       </c>
       <c r="J3" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
-        <v>8.109999999999999</v>
+        <v>425.72</v>
       </c>
       <c r="N3" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="O3" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -4807,71 +3703,71 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>122537</v>
+        <v>122232</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>YAGO RODRIGUES DA SILVA</t>
+          <t>MARCELO RAMADA DE JESUS</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>21:03</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="T3" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B4" t="n">
-        <v>854469</v>
+        <v>854612</v>
       </c>
       <c r="C4" t="n">
-        <v>465489</v>
+        <v>459841</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>CANETA ESF CIS SPIRO SORT 24UN</t>
+          <t>AMENDOIM DORI 320GR ORIGINAL</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3417051244</v>
+        <v>4753005395</v>
       </c>
       <c r="F4" t="n">
         <v>2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>88,46</t>
+          <t>21,56</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="I4" t="n">
-        <v>8</v>
+        <v>69</v>
       </c>
       <c r="J4" t="n">
-        <v>201</v>
+        <v>104</v>
       </c>
       <c r="K4" t="n">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="L4" t="n">
         <v>2</v>
       </c>
       <c r="M4" t="n">
-        <v>88.45999999999999</v>
+        <v>21.56</v>
       </c>
       <c r="N4" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -4879,71 +3775,71 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>181203</v>
+        <v>122537</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>JANAINA SOUSA PAIXAO</t>
+          <t>YAGO RODRIGUES DA SILVA</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>22:20</t>
+          <t>04:13</t>
         </is>
       </c>
       <c r="T4" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B5" t="n">
-        <v>854489</v>
+        <v>854656</v>
       </c>
       <c r="C5" t="n">
-        <v>476790</v>
+        <v>455159</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CHOC FERRERO KINDER BUENO DARK 43GR T2</t>
+          <t>AMENDOIM BONISSIMO 1,010KG TORRADO GRANU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1826041482</v>
+        <v>5670002263</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>329,38</t>
+          <t>54,42</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>60</v>
+        <v>12</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>89</v>
       </c>
       <c r="J5" t="n">
-        <v>723</v>
+        <v>102</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="L5" t="n">
         <v>2</v>
       </c>
       <c r="M5" t="n">
-        <v>329.38</v>
+        <v>54.42</v>
       </c>
       <c r="N5" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -4960,62 +3856,62 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>21:51</t>
+          <t>04:55</t>
         </is>
       </c>
       <c r="T5" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B6" t="n">
-        <v>854472</v>
+        <v>854596</v>
       </c>
       <c r="C6" t="n">
-        <v>465489</v>
+        <v>459841</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CANETA ESF CIS SPIRO SORT 24UN</t>
+          <t>AMENDOIM DORI 320GR ORIGINAL</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5968000257</v>
+        <v>1029073179</v>
       </c>
       <c r="F6" t="n">
+        <v>6</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>64,68</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>11</v>
+      </c>
+      <c r="I6" t="n">
+        <v>69</v>
+      </c>
+      <c r="J6" t="n">
+        <v>104</v>
+      </c>
+      <c r="K6" t="n">
+        <v>9</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="N6" t="n">
         <v>2</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>96,62</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>32</v>
-      </c>
-      <c r="I6" t="n">
-        <v>8</v>
-      </c>
-      <c r="J6" t="n">
-        <v>201</v>
-      </c>
-      <c r="K6" t="n">
-        <v>42</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>48.31</v>
-      </c>
-      <c r="N6" t="n">
-        <v>22</v>
-      </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -5023,71 +3919,71 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>181203</v>
+        <v>122537</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>JANAINA SOUSA PAIXAO</t>
+          <t>YAGO RODRIGUES DA SILVA</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>22:03</t>
+          <t>02:50</t>
         </is>
       </c>
       <c r="T6" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B7" t="n">
-        <v>854472</v>
+        <v>854594</v>
       </c>
       <c r="C7" t="n">
-        <v>465489</v>
+        <v>455159</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CANETA ESF CIS SPIRO SORT 24UN</t>
+          <t>AMENDOIM BONISSIMO 1,010KG TORRADO GRANU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5968000260</v>
+        <v>4030016125</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>46,08</t>
+          <t>49,80</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="I7" t="n">
-        <v>8</v>
+        <v>89</v>
       </c>
       <c r="J7" t="n">
-        <v>201</v>
+        <v>102</v>
       </c>
       <c r="K7" t="n">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>46.08</v>
+        <v>49.8</v>
       </c>
       <c r="N7" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
-        <v>3</v>
+        <v>59</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -5095,56 +3991,56 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>181203</v>
+        <v>122537</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>JANAINA SOUSA PAIXAO</t>
+          <t>YAGO RODRIGUES DA SILVA</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>22:03</t>
+          <t>01:59</t>
         </is>
       </c>
       <c r="T7" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B8" t="n">
-        <v>854453</v>
+        <v>854669</v>
       </c>
       <c r="C8" t="n">
-        <v>420215</v>
+        <v>461619</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BALAO SAO ROQUE 7 ROSA TUTI FRUTI 50UN</t>
+          <t>UD TACA VDO AGUA NADIR 340ML BRISTO 0011</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3756059667</v>
+        <v>1353114349</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>77,13</t>
+          <t>272,88</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="J8" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K8" t="n">
         <v>3</v>
@@ -5153,13 +4049,13 @@
         <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>77.13</v>
+        <v>136.44</v>
       </c>
       <c r="N8" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="O8" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -5176,62 +4072,62 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>21:47</t>
+          <t>05:43</t>
         </is>
       </c>
       <c r="T8" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B9" t="n">
-        <v>854474</v>
+        <v>854670</v>
       </c>
       <c r="C9" t="n">
-        <v>472113</v>
+        <v>467985</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LUVA VABENE NITRILICA PRETA M 100UN</t>
+          <t>FRALDA MAMYPOKO CALCA AZUL REGULAR RN 20</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5141006234</v>
+        <v>5597001225</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>46,76</t>
+          <t>128,83</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I9" t="n">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="J9" t="n">
-        <v>204</v>
+        <v>103</v>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>23.38</v>
+        <v>128.83</v>
       </c>
       <c r="N9" t="n">
+        <v>6</v>
+      </c>
+      <c r="O9" t="n">
         <v>23</v>
-      </c>
-      <c r="O9" t="n">
-        <v>8</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -5248,62 +4144,62 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>23:08</t>
+          <t>06:23</t>
         </is>
       </c>
       <c r="T9" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B10" t="n">
-        <v>854439</v>
+        <v>854673</v>
       </c>
       <c r="C10" t="n">
-        <v>441861</v>
+        <v>463671</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MANGUEIRA BARIFLEX TRANC VERDE 30MT</t>
+          <t>SABAO PO ASSIM 800GR BICARBONATO</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1070123305</v>
+        <v>4124015977</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>109,08</t>
+          <t>142,66</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="I10" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="J10" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>54.54</v>
+        <v>142.66</v>
       </c>
       <c r="N10" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -5311,71 +4207,71 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>122537</v>
+        <v>180121</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>YAGO RODRIGUES DA SILVA</t>
+          <t>TAINA MEDEIROS RIBEIRO</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>22:22</t>
+          <t>03:09</t>
         </is>
       </c>
       <c r="T10" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B11" t="n">
-        <v>854503</v>
+        <v>854637</v>
       </c>
       <c r="C11" t="n">
-        <v>472236</v>
+        <v>463671</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>SAND HAV BRASIL  LOGO AMARELO VERDE 37/8</t>
+          <t>SABAO PO ASSIM 800GR BICARBONATO</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5781001649</v>
+        <v>1678075295</v>
       </c>
       <c r="F11" t="n">
         <v>1</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>41,04</t>
+          <t>132,12</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="I11" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="J11" t="n">
-        <v>204</v>
+        <v>101</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
         <v>1</v>
       </c>
       <c r="M11" t="n">
-        <v>41.04</v>
+        <v>132.12</v>
       </c>
       <c r="N11" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="O11" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -5383,71 +4279,71 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>180185</v>
+        <v>180121</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>ALEANDRA TRINDADE SOUSA</t>
+          <t>TAINA MEDEIROS RIBEIRO</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>22:11</t>
+          <t>02:16</t>
         </is>
       </c>
       <c r="T11" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B12" t="n">
-        <v>854448</v>
+        <v>854658</v>
       </c>
       <c r="C12" t="n">
-        <v>472238</v>
+        <v>459841</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>SAND HAV BRASIL  LOGO AMARELO VERDE 41/2</t>
+          <t>AMENDOIM DORI 320GR ORIGINAL</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2828054732</v>
+        <v>1664041413</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>40,19</t>
+          <t>65,34</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="I12" t="n">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="J12" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="K12" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M12" t="n">
-        <v>40.19</v>
+        <v>65.34</v>
       </c>
       <c r="N12" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="O12" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -5455,71 +4351,71 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>122618</v>
+        <v>122537</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>WEBERT JOSE DA SILVA</t>
+          <t>YAGO RODRIGUES DA SILVA</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>21:28</t>
+          <t>02:50</t>
         </is>
       </c>
       <c r="T12" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B13" t="n">
-        <v>854440</v>
+        <v>854608</v>
       </c>
       <c r="C13" t="n">
-        <v>472238</v>
+        <v>436036</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SAND HAV BRASIL  LOGO AMARELO VERDE 41/2</t>
+          <t>SAND HAV BRASIL  LOGO BCO 35/6</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4196028577</v>
+        <v>5974000047</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>40,48</t>
+          <t>121,44</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I13" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="J13" t="n">
-        <v>102</v>
+        <v>203</v>
       </c>
       <c r="K13" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M13" t="n">
-        <v>40.48</v>
+        <v>121.44</v>
       </c>
       <c r="N13" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="O13" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -5527,71 +4423,71 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>122574</v>
+        <v>180185</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>LEILIENE DO BOM PARTO SOUSA COSTA</t>
+          <t>ALEANDRA TRINDADE SOUSA</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>23:36</t>
+          <t>02:07</t>
         </is>
       </c>
       <c r="T13" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B14" t="n">
-        <v>854448</v>
+        <v>854608</v>
       </c>
       <c r="C14" t="n">
-        <v>472237</v>
+        <v>436036</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SAND HAV BRASIL  LOGO AMARELO VERDE 39/0</t>
+          <t>SAND HAV BRASIL  LOGO BCO 35/6</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2828054732</v>
+        <v>5974000051</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>40,19</t>
+          <t>41,24</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I14" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="J14" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K14" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="L14" t="n">
         <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>40.19</v>
+        <v>41.24</v>
       </c>
       <c r="N14" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="O14" t="n">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -5599,71 +4495,71 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>122618</v>
+        <v>181255</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>WEBERT JOSE DA SILVA</t>
+          <t>DANIELE AIRES MOREIRA</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>21:27</t>
+          <t>02:55</t>
         </is>
       </c>
       <c r="T14" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B15" t="n">
-        <v>854440</v>
+        <v>854595</v>
       </c>
       <c r="C15" t="n">
-        <v>472237</v>
+        <v>459742</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SAND HAV BRASIL  LOGO AMARELO VERDE 39/0</t>
+          <t>VIN NAC PERGOLA 750ML BCO SECO</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4196028577</v>
+        <v>5560002994</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>40,48</t>
+          <t>93,00</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="I15" t="n">
-        <v>14</v>
+        <v>106</v>
       </c>
       <c r="J15" t="n">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K15" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="L15" t="n">
         <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>40.48</v>
+        <v>15.5</v>
       </c>
       <c r="N15" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="O15" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -5671,71 +4567,71 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>122574</v>
+        <v>180121</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>LEILIENE DO BOM PARTO SOUSA COSTA</t>
+          <t>TAINA MEDEIROS RIBEIRO</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>02:15</t>
         </is>
       </c>
       <c r="T15" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B16" t="n">
-        <v>854469</v>
+        <v>854594</v>
       </c>
       <c r="C16" t="n">
-        <v>469865</v>
+        <v>420215</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>REPELENTE OFF SPRAY 170ML FAMILY</t>
+          <t>BALAO SAO ROQUE 7 ROSA TUTI FRUTI 50UN</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3417051242</v>
+        <v>1591030747</v>
       </c>
       <c r="F16" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>199,60</t>
+          <t>77,66</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="J16" t="n">
-        <v>1.001</v>
+        <v>102</v>
       </c>
       <c r="K16" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="L16" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
-        <v>199.6</v>
+        <v>77.66</v>
       </c>
       <c r="N16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -5743,71 +4639,71 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>181332</v>
+        <v>122537</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>NAYARA PEREIRA ROSA</t>
+          <t>YAGO RODRIGUES DA SILVA</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>22:44</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="T16" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B17" t="n">
-        <v>854459</v>
+        <v>854629</v>
       </c>
       <c r="C17" t="n">
-        <v>461740</v>
+        <v>427994</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>BISC MARIL TORTINHA 300GR CHOCOLATE</t>
+          <t>AZEITE E VIRG PORT ANDORINHA 500ML VIDRO</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3687032448</v>
+        <v>4718014077</v>
       </c>
       <c r="F17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>149,63</t>
+          <t>82,35</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I17" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="J17" t="n">
         <v>101</v>
       </c>
       <c r="K17" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="L17" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M17" t="n">
-        <v>149.63</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="O17" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -5824,62 +4720,62 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>21:02</t>
+          <t>04:19</t>
         </is>
       </c>
       <c r="T17" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B18" t="n">
-        <v>854453</v>
+        <v>854612</v>
       </c>
       <c r="C18" t="n">
-        <v>454255</v>
+        <v>461544</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>AMAC COMFORT 500ML CONC C ESSENC AZ</t>
+          <t>BISC NESTLE 60GR COOKIES CLASSIC BAUN</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1836021975</v>
+        <v>5648006579</v>
       </c>
       <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>135,44</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
         <v>2</v>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>20,72</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>26</v>
-      </c>
       <c r="I18" t="n">
-        <v>17</v>
+        <v>104</v>
       </c>
       <c r="J18" t="n">
         <v>101</v>
       </c>
       <c r="K18" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>20.72</v>
+        <v>135.44</v>
       </c>
       <c r="N18" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="O18" t="n">
-        <v>49</v>
+        <v>6</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
@@ -5896,62 +4792,62 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>21:49</t>
+          <t>04:06</t>
         </is>
       </c>
       <c r="T18" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B19" t="n">
-        <v>854469</v>
+        <v>854625</v>
       </c>
       <c r="C19" t="n">
-        <v>455159</v>
+        <v>454948</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>AMENDOIM BONISSIMO 1,010KG TORRADO GRANU</t>
+          <t>KIMELEKA ACRILEX 180GR SORTIDA</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5811001424</v>
+        <v>4132035144</v>
       </c>
       <c r="F19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>108,48</t>
+          <t>75,91</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="I19" t="n">
-        <v>89</v>
+        <v>16</v>
       </c>
       <c r="J19" t="n">
         <v>102</v>
       </c>
       <c r="K19" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M19" t="n">
-        <v>81.36</v>
+        <v>75.91</v>
       </c>
       <c r="N19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O19" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -5968,62 +4864,62 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>02:11</t>
+          <t>04:22</t>
         </is>
       </c>
       <c r="T19" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B20" t="n">
-        <v>854502</v>
+        <v>854673</v>
       </c>
       <c r="C20" t="n">
-        <v>420215</v>
+        <v>468083</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>BALAO SAO ROQUE 7 ROSA TUTI FRUTI 50UN</t>
+          <t>CREME DE AVELA NUTELLA FERRERO 350GR RTD</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5157004873</v>
+        <v>2424052389</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>77,13</t>
+          <t>1.259,40</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>18</v>
+        <v>200</v>
       </c>
       <c r="I20" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J20" t="n">
         <v>102</v>
       </c>
       <c r="K20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>77.13</v>
+        <v>1259.4</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O20" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
@@ -6031,20 +4927,20 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>122537</v>
+        <v>180185</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>YAGO RODRIGUES DA SILVA</t>
+          <t>ALEANDRA TRINDADE SOUSA</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>00:50</t>
+          <t>04:48</t>
         </is>
       </c>
       <c r="T20" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
     </row>
   </sheetData>
